--- a/lab-standards/AEOSIB-lab-standard.xlsx
+++ b/lab-standards/AEOSIB-lab-standard.xlsx
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F19" s="27">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -729,7 +729,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F20" s="27">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -777,7 +777,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F22" s="27">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -849,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F25" s="27">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F26" s="27">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F27" s="27">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>

--- a/lab-standards/AEOSIB-lab-standard.xlsx
+++ b/lab-standards/AEOSIB-lab-standard.xlsx
@@ -1208,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F19" s="27">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -1232,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" s="27">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -1352,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F25" s="27">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F28" s="27">
         <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
@@ -1448,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F29" s="27">
         <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
@@ -1472,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F30" s="27">
         <f>IFERROR(MIN(C30,D30)*E30/C30,0)</f>
@@ -1496,7 +1496,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F31" s="27">
         <f>IFERROR(MIN(C31,D31)*E31/C31,0)</f>
